--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d290b837e37e767/Documents/GitHub/CONCURSO/CATALOGO_DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31366131-8239-40FE-B72F-8106B003967A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94AFCE3D-55C5-4993-BDB4-FE3F9652B751}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="675" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>licencia</t>
   </si>
@@ -60,9 +60,6 @@
     <t>https://transport.opendatasoft.com/explore/dataset/estaciones-de-transmilenio</t>
   </si>
   <si>
-    <t>https://www.datos.gov.co/Educaci-n/LISTADO-COLEGIOS-BOGOTA/qijw-htwa</t>
-  </si>
-  <si>
     <t>Secretaría Distrital de Planeación – IDECA</t>
   </si>
   <si>
@@ -204,10 +201,10 @@
     <t xml:space="preserve">https://transport.opendatasoft.com/explore/dataset/estaciones-de-transmilenio </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.datos.gov.co/Educaci-n/LISTADO-COLEGIOS-BOGOTA/qijw-htwa/about_data </t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.datos.gov.co/dataset/-rea-actividad-POT-Bogot-D-C-/5iwv-ytzg/about_data </t>
+  </si>
+  <si>
+    <t>https://www.datos.gov.co/dataset/Colegios-Bogot-D-C-/y8ah-xz3u/about_data</t>
   </si>
 </sst>
 </file>
@@ -366,6 +363,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -674,16 +675,16 @@
   <sheetData>
     <row r="1" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
@@ -692,25 +693,25 @@
         <v>1</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -718,41 +719,41 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L2" s="3">
-        <f t="shared" ref="L2:L6" ca="1" si="0">TODAY()</f>
+        <f t="shared" ref="L2:L5" ca="1" si="0">TODAY()</f>
         <v>45988</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -760,41 +761,41 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" ca="1" si="0"/>
         <v>45988</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -802,41 +803,41 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" ca="1" si="0"/>
         <v>45988</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -847,38 +848,38 @@
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" ca="1" si="0"/>
         <v>45988</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -886,56 +887,54 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="L6" s="3">
         <v>45988</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{16F84D82-F471-4F81-9A21-4C11E29F0A26}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{F601D901-85D1-48B2-9732-7A11A2F7FD7A}"/>
-    <hyperlink ref="B2" r:id="rId6" xr:uid="{98D6329D-0666-4AE0-87F4-6C8B2A26ACB8}"/>
-    <hyperlink ref="B3" r:id="rId7" xr:uid="{75A5836C-FBC6-4386-AA52-4780E9D7091F}"/>
-    <hyperlink ref="B4" r:id="rId8" xr:uid="{ADB31B1D-6EBA-4F3A-A1D7-B8D2037B34CB}"/>
-    <hyperlink ref="B5" r:id="rId9" xr:uid="{E622A664-F806-4440-90FE-6A9EFBFF2347}"/>
-    <hyperlink ref="B6" r:id="rId10" xr:uid="{A1CDCD8F-3588-4FB2-AD4A-A44F213EBC81}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{16F84D82-F471-4F81-9A21-4C11E29F0A26}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{F601D901-85D1-48B2-9732-7A11A2F7FD7A}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{98D6329D-0666-4AE0-87F4-6C8B2A26ACB8}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{75A5836C-FBC6-4386-AA52-4780E9D7091F}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{ADB31B1D-6EBA-4F3A-A1D7-B8D2037B34CB}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{A1CDCD8F-3588-4FB2-AD4A-A44F213EBC81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId11"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId9"/>
 </worksheet>
 </file>
--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d290b837e37e767/Documents/GitHub/CONCURSO/CATALOGO_DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94AFCE3D-55C5-4993-BDB4-FE3F9652B751}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD837928-1EE9-42B6-9A2D-F96772C963AE}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="675" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>licencia</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>https://www.datos.gov.co/dataset/Colegios-Bogot-D-C-/y8ah-xz3u/about_data</t>
+  </si>
+  <si>
+    <t>https://datosabiertos.bogota.gov.co/dataset/colegios-bogota-d-c</t>
   </si>
 </sst>
 </file>
@@ -848,7 +851,7 @@
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>

--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="49" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD837928-1EE9-42B6-9A2D-F96772C963AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="L2" s="3">
         <f t="shared" ref="L2:L5" ca="1" si="0">TODAY()</f>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>49</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="L3" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>47</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="L4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>50</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>51</v>

--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="49" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD837928-1EE9-42B6-9A2D-F96772C963AE}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13230" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="L2" s="3">
         <f t="shared" ref="L2:L5" ca="1" si="0">TODAY()</f>
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>49</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="L3" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>47</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="L4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>50</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>51</v>

--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d290b837e37e767/Documents/GitHub/CONCURSO/CATALOGO_DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD837928-1EE9-42B6-9A2D-F96772C963AE}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F49D44E9-0A4A-45DC-87CF-A41117757613}"/>
   <bookViews>
-    <workbookView xWindow="13230" yWindow="270" windowWidth="14250" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="990" windowWidth="24000" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>licencia</t>
   </si>
@@ -99,24 +99,6 @@
     <t>Mensual</t>
   </si>
   <si>
-    <t>id_manzana, estrato, localidad, barrio</t>
-  </si>
-  <si>
-    <t>localidad, año, mes, delito, cantidad</t>
-  </si>
-  <si>
-    <t>estacion_id, nombre, lat, lon, portal</t>
-  </si>
-  <si>
-    <t>codigo_dane, nombre, direccion, localidad, naturaleza</t>
-  </si>
-  <si>
-    <t>id_poligono, actividad_predominante, area_m2</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>https://datosabiertos.bogota.gov.co/dataset/estratificacion-para-bogota</t>
   </si>
   <si>
@@ -132,12 +114,6 @@
     <t>extension</t>
   </si>
   <si>
-    <t>usar en modelo</t>
-  </si>
-  <si>
-    <t>ultima descarga</t>
-  </si>
-  <si>
     <t>frecuencia actualizacion</t>
   </si>
   <si>
@@ -168,9 +144,6 @@
     <t>Directorio de sedes educativas oficiales y privadas para análisis de cobertura.</t>
   </si>
   <si>
-    <t>variables clave</t>
-  </si>
-  <si>
     <t>data set despues de preparacion</t>
   </si>
   <si>
@@ -208,13 +181,40 @@
   </si>
   <si>
     <t>https://datosabiertos.bogota.gov.co/dataset/colegios-bogota-d-c</t>
+  </si>
+  <si>
+    <t>Red adscrita de salud para Bogotá D.C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.datos.gov.co/dataset/Red-adscrita-de-salud-para-Bogot-D-C-/sebg-us5f/about_data </t>
+  </si>
+  <si>
+    <t>Secretaria Distrital de Salud de Bogotá</t>
+  </si>
+  <si>
+    <t>dim_salud</t>
+  </si>
+  <si>
+    <t>directorio unidades medicas adscritas a la red de salud de bogota</t>
+  </si>
+  <si>
+    <t>Parques. POT Bogotá D.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.datos.gov.co/dataset/Parques-POT-Bogot-D-C-/m7rz-ihvn/about_data </t>
+  </si>
+  <si>
+    <t>dim_verde</t>
+  </si>
+  <si>
+    <t>directorio zonas verdes desde el POT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,8 +237,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,8 +257,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -279,8 +291,28 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE4E4E4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE4E4E4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -294,12 +326,30 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -309,12 +359,21 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -328,7 +387,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -336,16 +395,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +424,254 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -368,6 +686,25 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB59A8E1-AFEB-41CB-8678-2F8DB7A1E1A3}" name="Tabla1" displayName="Tabla1" ref="A1:J8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="12" tableBorderDxfId="13">
+  <autoFilter ref="A1:J8" xr:uid="{CB59A8E1-AFEB-41CB-8678-2F8DB7A1E1A3}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{5729762B-5AA5-4516-9CB3-35844BBCD8C0}" name="nombre dataset" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{06B1E74C-F4AF-45AE-967E-048F8D6E0FA3}" name="url datos abiertos " dataDxfId="10" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="3" xr3:uid="{153DB376-90FA-4D99-A209-1DEBD07E5F6B}" name="url fuente" dataDxfId="9" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="4" xr3:uid="{EA7530BE-32DC-4D2E-8349-87D4E2BC25F1}" name="autor entidad" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{D9F4F31D-5C7C-46D1-8C98-F44C507B3789}" name="licencia" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{981B5479-E7C8-43E7-BCA4-04D660DF4525}" name="formato" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{C3BBA145-F8D5-49E9-81C0-A600847A18AD}" name="extension" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{2487A416-849B-42F1-B6E6-788044F1EFC2}" name="frecuencia actualizacion" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{09101341-7BF8-4139-99BE-90A9F11A4333}" name="descripcion funcional " dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{6953B9D4-0DAE-442B-8A52-3A438893C911}" name="data set despues de preparacion" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -660,72 +997,61 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="28.28515625" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" customWidth="1"/>
+    <col min="10" max="10" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>9</v>
@@ -734,37 +1060,27 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="3">
-        <f t="shared" ref="L2:L5" ca="1" si="0">TODAY()</f>
-        <v>45990</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
@@ -776,37 +1092,27 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>47</v>
+        <v>32</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
@@ -827,31 +1133,21 @@
         <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -869,31 +1165,21 @@
         <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="3">
-        <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
@@ -902,28 +1188,83 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="3">
-        <v>45988</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -936,8 +1277,15 @@
     <hyperlink ref="B3" r:id="rId6" xr:uid="{75A5836C-FBC6-4386-AA52-4780E9D7091F}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{ADB31B1D-6EBA-4F3A-A1D7-B8D2037B34CB}"/>
     <hyperlink ref="B6" r:id="rId8" xr:uid="{A1CDCD8F-3588-4FB2-AD4A-A44F213EBC81}"/>
+    <hyperlink ref="B7" r:id="rId9" xr:uid="{D5B981ED-8404-4043-9E96-34B04056943C}"/>
+    <hyperlink ref="C7" r:id="rId10" xr:uid="{A8EDB5EF-7C35-458F-A5DF-832B06506A60}"/>
+    <hyperlink ref="B8" r:id="rId11" xr:uid="{B8A6E227-1893-4C28-B4CE-5A8360032ADF}"/>
+    <hyperlink ref="C8" r:id="rId12" xr:uid="{D5C4137A-0054-4B0E-B903-395A0C31E4D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId9"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId13"/>
+  <tableParts count="1">
+    <tablePart r:id="rId14"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/CATALOGO_DATOS/catalogo_datos.xlsx
+++ b/CATALOGO_DATOS/catalogo_datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d290b837e37e767/Documents/GitHub/CONCURSO/CATALOGO_DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F49D44E9-0A4A-45DC-87CF-A41117757613}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{8BF656C8-66F2-46DE-9CAC-33F1F4976620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C287D3AF-D697-40E2-9695-8219FA39BDFA}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="990" windowWidth="24000" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CATALOGO" sheetId="1" r:id="rId1"/>
@@ -395,7 +395,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -407,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -425,6 +425,217 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -460,217 +671,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -689,19 +689,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB59A8E1-AFEB-41CB-8678-2F8DB7A1E1A3}" name="Tabla1" displayName="Tabla1" ref="A1:J8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="12" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB59A8E1-AFEB-41CB-8678-2F8DB7A1E1A3}" name="Tabla1" displayName="Tabla1" ref="A1:J8" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <autoFilter ref="A1:J8" xr:uid="{CB59A8E1-AFEB-41CB-8678-2F8DB7A1E1A3}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{5729762B-5AA5-4516-9CB3-35844BBCD8C0}" name="nombre dataset" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{06B1E74C-F4AF-45AE-967E-048F8D6E0FA3}" name="url datos abiertos " dataDxfId="10" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="3" xr3:uid="{153DB376-90FA-4D99-A209-1DEBD07E5F6B}" name="url fuente" dataDxfId="9" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="4" xr3:uid="{EA7530BE-32DC-4D2E-8349-87D4E2BC25F1}" name="autor entidad" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D9F4F31D-5C7C-46D1-8C98-F44C507B3789}" name="licencia" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{981B5479-E7C8-43E7-BCA4-04D660DF4525}" name="formato" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{C3BBA145-F8D5-49E9-81C0-A600847A18AD}" name="extension" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{2487A416-849B-42F1-B6E6-788044F1EFC2}" name="frecuencia actualizacion" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{09101341-7BF8-4139-99BE-90A9F11A4333}" name="descripcion funcional " dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{6953B9D4-0DAE-442B-8A52-3A438893C911}" name="data set despues de preparacion" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5729762B-5AA5-4516-9CB3-35844BBCD8C0}" name="nombre dataset" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{06B1E74C-F4AF-45AE-967E-048F8D6E0FA3}" name="url datos abiertos " dataDxfId="8" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="3" xr3:uid="{153DB376-90FA-4D99-A209-1DEBD07E5F6B}" name="url fuente" dataDxfId="7" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="4" xr3:uid="{EA7530BE-32DC-4D2E-8349-87D4E2BC25F1}" name="autor entidad" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{D9F4F31D-5C7C-46D1-8C98-F44C507B3789}" name="licencia" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{981B5479-E7C8-43E7-BCA4-04D660DF4525}" name="formato" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{C3BBA145-F8D5-49E9-81C0-A600847A18AD}" name="extension" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{2487A416-849B-42F1-B6E6-788044F1EFC2}" name="frecuencia actualizacion" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{09101341-7BF8-4139-99BE-90A9F11A4333}" name="descripcion funcional " dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{6953B9D4-0DAE-442B-8A52-3A438893C911}" name="data set despues de preparacion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1075,7 +1075,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>50</v>
       </c>
@@ -1281,11 +1281,13 @@
     <hyperlink ref="C7" r:id="rId10" xr:uid="{A8EDB5EF-7C35-458F-A5DF-832B06506A60}"/>
     <hyperlink ref="B8" r:id="rId11" xr:uid="{B8A6E227-1893-4C28-B4CE-5A8360032ADF}"/>
     <hyperlink ref="C8" r:id="rId12" xr:uid="{D5C4137A-0054-4B0E-B903-395A0C31E4D8}"/>
+    <hyperlink ref="B5" r:id="rId13" xr:uid="{EB415C70-5C42-41FF-8935-2602790C3AB3}"/>
+    <hyperlink ref="C5" r:id="rId14" xr:uid="{33A4F23E-4A98-49D2-9CCB-F740DB42B484}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId13"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>